--- a/pipeline/credit_rating/output/xhtn_tong_hop_20261006.xlsx
+++ b/pipeline/credit_rating/output/xhtn_tong_hop_20261006.xlsx
@@ -685,7 +685,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -1127,7 +1127,7 @@
       <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -1351,7 +1351,7 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -1457,7 +1457,7 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -1573,7 +1573,7 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>2026-10-06 10:43:02</t>
+          <t>2026-10-06 15:24:42</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -1803,7 +1803,7 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:47</t>
+          <t>2026-10-06 15:24:28</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -2023,7 +2023,7 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -2111,7 +2111,7 @@
       <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -2233,7 +2233,7 @@
       <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -2343,7 +2343,7 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -2457,7 +2457,7 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -2571,7 +2571,7 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -2655,7 +2655,7 @@
       <c r="AD20" t="inlineStr"/>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -2739,7 +2739,7 @@
       <c r="AD21" t="inlineStr"/>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -2973,7 +2973,7 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -3083,7 +3083,7 @@
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
@@ -3215,7 +3215,7 @@
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
@@ -3343,7 +3343,7 @@
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
@@ -3449,7 +3449,7 @@
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
@@ -3555,7 +3555,7 @@
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
@@ -3665,7 +3665,7 @@
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
@@ -3793,7 +3793,7 @@
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
@@ -3903,7 +3903,7 @@
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
@@ -3991,7 +3991,7 @@
       <c r="AD32" t="inlineStr"/>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
@@ -4079,7 +4079,7 @@
       <c r="AD33" t="inlineStr"/>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
@@ -4309,7 +4309,7 @@
       </c>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF35" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="AE36" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF36" t="inlineStr">
@@ -4539,7 +4539,7 @@
       </c>
       <c r="AE37" t="inlineStr">
         <is>
-          <t>2026-10-06 10:43:02</t>
+          <t>2026-10-06 15:24:42</t>
         </is>
       </c>
       <c r="AF37" t="inlineStr">
@@ -4649,7 +4649,7 @@
       <c r="AD38" t="inlineStr"/>
       <c r="AE38" t="inlineStr">
         <is>
-          <t>2026-10-06 10:43:02</t>
+          <t>2026-10-06 15:24:42</t>
         </is>
       </c>
       <c r="AF38" t="inlineStr">
@@ -4765,7 +4765,7 @@
       </c>
       <c r="AE39" t="inlineStr">
         <is>
-          <t>2026-10-06 10:43:02</t>
+          <t>2026-10-06 15:24:42</t>
         </is>
       </c>
       <c r="AF39" t="inlineStr">
@@ -4875,7 +4875,7 @@
       <c r="AD40" t="inlineStr"/>
       <c r="AE40" t="inlineStr">
         <is>
-          <t>2026-10-06 10:43:02</t>
+          <t>2026-10-06 15:24:42</t>
         </is>
       </c>
       <c r="AF40" t="inlineStr">
@@ -5003,7 +5003,7 @@
       </c>
       <c r="AE41" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF41" t="inlineStr">
@@ -5117,7 +5117,7 @@
       </c>
       <c r="AE42" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF42" t="inlineStr">
@@ -5231,7 +5231,7 @@
       </c>
       <c r="AE43" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF43" t="inlineStr">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="AE44" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF44" t="inlineStr">
@@ -5465,7 +5465,7 @@
       </c>
       <c r="AE45" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF45" t="inlineStr">
@@ -5579,7 +5579,7 @@
       </c>
       <c r="AE46" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF46" t="inlineStr">
@@ -5693,7 +5693,7 @@
       </c>
       <c r="AE47" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF47" t="inlineStr">
@@ -5809,7 +5809,7 @@
       </c>
       <c r="AE48" t="inlineStr">
         <is>
-          <t>2026-10-06 10:43:02</t>
+          <t>2026-10-06 15:24:42</t>
         </is>
       </c>
       <c r="AF48" t="inlineStr">
@@ -5923,7 +5923,7 @@
       </c>
       <c r="AE49" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF49" t="inlineStr">
@@ -6033,7 +6033,7 @@
       </c>
       <c r="AE50" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF50" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="AE51" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF51" t="inlineStr">
@@ -6273,7 +6273,7 @@
       </c>
       <c r="AE52" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF52" t="inlineStr">
@@ -6387,7 +6387,7 @@
       </c>
       <c r="AE53" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF53" t="inlineStr">
@@ -6507,7 +6507,7 @@
       </c>
       <c r="AE54" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF54" t="inlineStr">
@@ -6621,7 +6621,7 @@
       </c>
       <c r="AE55" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF55" t="inlineStr">
@@ -6731,7 +6731,7 @@
       </c>
       <c r="AE56" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF56" t="inlineStr">
@@ -6847,7 +6847,7 @@
       </c>
       <c r="AE57" t="inlineStr">
         <is>
-          <t>2026-10-06 10:43:02</t>
+          <t>2026-10-06 15:24:42</t>
         </is>
       </c>
       <c r="AF57" t="inlineStr">
@@ -6957,7 +6957,7 @@
       </c>
       <c r="AE58" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF58" t="inlineStr">
@@ -7067,7 +7067,7 @@
       </c>
       <c r="AE59" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF59" t="inlineStr">
@@ -7191,7 +7191,7 @@
       </c>
       <c r="AE60" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF60" t="inlineStr">
@@ -7301,7 +7301,7 @@
       </c>
       <c r="AE61" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF61" t="inlineStr">
@@ -7411,7 +7411,7 @@
       </c>
       <c r="AE62" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF62" t="inlineStr">
@@ -7521,7 +7521,7 @@
       </c>
       <c r="AE63" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF63" t="inlineStr">
@@ -7621,7 +7621,7 @@
       </c>
       <c r="AE64" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF64" t="inlineStr">
@@ -7731,7 +7731,7 @@
       </c>
       <c r="AE65" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF65" t="inlineStr">
@@ -7841,7 +7841,7 @@
       </c>
       <c r="AE66" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF66" t="inlineStr">
@@ -7951,7 +7951,7 @@
       </c>
       <c r="AE67" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF67" t="inlineStr">
@@ -8067,7 +8067,7 @@
       </c>
       <c r="AE68" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF68" t="inlineStr">
@@ -8199,7 +8199,7 @@
       </c>
       <c r="AE69" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF69" t="inlineStr">
@@ -8327,7 +8327,7 @@
       </c>
       <c r="AE70" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF70" t="inlineStr">
@@ -8459,7 +8459,7 @@
       </c>
       <c r="AE71" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF71" t="inlineStr">
@@ -8587,7 +8587,7 @@
       </c>
       <c r="AE72" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF72" t="inlineStr">
@@ -8697,7 +8697,7 @@
       </c>
       <c r="AE73" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF73" t="inlineStr">
@@ -8809,7 +8809,7 @@
       </c>
       <c r="AE74" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF74" t="inlineStr">
@@ -8925,7 +8925,7 @@
       </c>
       <c r="AE75" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF75" t="inlineStr">
@@ -9039,7 +9039,7 @@
       </c>
       <c r="AE76" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF76" t="inlineStr">
@@ -9159,7 +9159,7 @@
       </c>
       <c r="AE77" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF77" t="inlineStr">
@@ -9259,7 +9259,7 @@
       </c>
       <c r="AE78" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF78" t="inlineStr">
@@ -9373,7 +9373,7 @@
       </c>
       <c r="AE79" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF79" t="inlineStr">
@@ -9489,7 +9489,7 @@
       </c>
       <c r="AE80" t="inlineStr">
         <is>
-          <t>2026-10-06 10:43:02</t>
+          <t>2026-10-06 15:24:42</t>
         </is>
       </c>
       <c r="AF80" t="inlineStr">
@@ -9599,7 +9599,7 @@
       </c>
       <c r="AE81" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF81" t="inlineStr">
@@ -9713,7 +9713,7 @@
       </c>
       <c r="AE82" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF82" t="inlineStr">
@@ -9827,7 +9827,7 @@
       </c>
       <c r="AE83" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF83" t="inlineStr">
@@ -9955,7 +9955,7 @@
       </c>
       <c r="AE84" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF84" t="inlineStr">
@@ -10071,7 +10071,7 @@
       </c>
       <c r="AE85" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF85" t="inlineStr">
@@ -10167,7 +10167,7 @@
       </c>
       <c r="AE86" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF86" t="inlineStr">
@@ -10277,7 +10277,7 @@
       </c>
       <c r="AE87" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF87" t="inlineStr">
@@ -10377,7 +10377,7 @@
       </c>
       <c r="AE88" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF88" t="inlineStr">
@@ -10491,7 +10491,7 @@
       </c>
       <c r="AE89" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF89" t="inlineStr">
@@ -10605,7 +10605,7 @@
       </c>
       <c r="AE90" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF90" t="inlineStr">
@@ -10705,7 +10705,7 @@
       </c>
       <c r="AE91" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF91" t="inlineStr">
@@ -10819,7 +10819,7 @@
       </c>
       <c r="AE92" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:47</t>
+          <t>2026-10-06 15:24:28</t>
         </is>
       </c>
       <c r="AF92" t="inlineStr">
@@ -10929,7 +10929,7 @@
       </c>
       <c r="AE93" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF93" t="inlineStr">
@@ -11043,7 +11043,7 @@
       </c>
       <c r="AE94" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF94" t="inlineStr">
@@ -11157,7 +11157,7 @@
       </c>
       <c r="AE95" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF95" t="inlineStr">
@@ -11267,7 +11267,7 @@
       </c>
       <c r="AE96" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF96" t="inlineStr">
@@ -11381,7 +11381,7 @@
       </c>
       <c r="AE97" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF97" t="inlineStr">
@@ -11495,7 +11495,7 @@
       </c>
       <c r="AE98" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:47</t>
+          <t>2026-10-06 15:24:28</t>
         </is>
       </c>
       <c r="AF98" t="inlineStr">
@@ -11609,7 +11609,7 @@
       </c>
       <c r="AE99" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:47</t>
+          <t>2026-10-06 15:24:28</t>
         </is>
       </c>
       <c r="AF99" t="inlineStr">
@@ -11733,7 +11733,7 @@
       </c>
       <c r="AE100" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:49</t>
+          <t>2026-10-06 15:24:30</t>
         </is>
       </c>
       <c r="AF100" t="inlineStr">
@@ -11843,7 +11843,7 @@
       </c>
       <c r="AE101" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF101" t="inlineStr">
@@ -11957,7 +11957,7 @@
       </c>
       <c r="AE102" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF102" t="inlineStr">
@@ -12071,7 +12071,7 @@
       </c>
       <c r="AE103" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF103" t="inlineStr">
@@ -12185,7 +12185,7 @@
       </c>
       <c r="AE104" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF104" t="inlineStr">
@@ -12297,7 +12297,7 @@
       </c>
       <c r="AE105" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF105" t="inlineStr">
@@ -12413,7 +12413,7 @@
       </c>
       <c r="AE106" t="inlineStr">
         <is>
-          <t>2026-10-06 10:43:02</t>
+          <t>2026-10-06 15:24:42</t>
         </is>
       </c>
       <c r="AF106" t="inlineStr">
@@ -12523,7 +12523,7 @@
       </c>
       <c r="AE107" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF107" t="inlineStr">
@@ -12633,7 +12633,7 @@
       </c>
       <c r="AE108" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF108" t="inlineStr">
@@ -12751,7 +12751,7 @@
       </c>
       <c r="AE109" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:47</t>
+          <t>2026-10-06 15:24:28</t>
         </is>
       </c>
       <c r="AF109" t="inlineStr">
@@ -12875,7 +12875,7 @@
       </c>
       <c r="AE110" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF110" t="inlineStr">
@@ -12995,7 +12995,7 @@
       </c>
       <c r="AE111" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF111" t="inlineStr">
@@ -13115,7 +13115,7 @@
       </c>
       <c r="AE112" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF112" t="inlineStr">
@@ -13247,7 +13247,7 @@
       </c>
       <c r="AE113" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF113" t="inlineStr">
@@ -13371,7 +13371,7 @@
       </c>
       <c r="AE114" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF114" t="inlineStr">
@@ -13495,7 +13495,7 @@
       </c>
       <c r="AE115" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF115" t="inlineStr">
@@ -13595,7 +13595,7 @@
       </c>
       <c r="AE116" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF116" t="inlineStr">
@@ -13715,7 +13715,7 @@
       </c>
       <c r="AE117" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF117" t="inlineStr">
@@ -13843,7 +13843,7 @@
       </c>
       <c r="AE118" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF118" t="inlineStr">
@@ -13957,7 +13957,7 @@
       </c>
       <c r="AE119" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF119" t="inlineStr">
@@ -14071,7 +14071,7 @@
       </c>
       <c r="AE120" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF120" t="inlineStr">
@@ -14185,7 +14185,7 @@
       </c>
       <c r="AE121" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF121" t="inlineStr">
@@ -14295,7 +14295,7 @@
       </c>
       <c r="AE122" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF122" t="inlineStr">
@@ -14409,7 +14409,7 @@
       </c>
       <c r="AE123" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF123" t="inlineStr">
@@ -14523,7 +14523,7 @@
       </c>
       <c r="AE124" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF124" t="inlineStr">
@@ -14637,7 +14637,7 @@
       </c>
       <c r="AE125" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF125" t="inlineStr">
@@ -14751,7 +14751,7 @@
       </c>
       <c r="AE126" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF126" t="inlineStr">
@@ -14871,7 +14871,7 @@
       </c>
       <c r="AE127" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF127" t="inlineStr">
@@ -14987,7 +14987,7 @@
       </c>
       <c r="AE128" t="inlineStr">
         <is>
-          <t>2026-10-06 10:43:02</t>
+          <t>2026-10-06 15:24:42</t>
         </is>
       </c>
       <c r="AF128" t="inlineStr">
@@ -15097,7 +15097,7 @@
       </c>
       <c r="AE129" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF129" t="inlineStr">
@@ -15217,7 +15217,7 @@
       </c>
       <c r="AE130" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF130" t="inlineStr">
@@ -15349,7 +15349,7 @@
       </c>
       <c r="AE131" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF131" t="inlineStr">
@@ -15477,7 +15477,7 @@
       </c>
       <c r="AE132" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF132" t="inlineStr">
@@ -15589,7 +15589,7 @@
       </c>
       <c r="AE133" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF133" t="inlineStr">
@@ -15699,7 +15699,7 @@
       </c>
       <c r="AE134" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF134" t="inlineStr">
@@ -15809,7 +15809,7 @@
       </c>
       <c r="AE135" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF135" t="inlineStr">
@@ -15919,7 +15919,7 @@
       </c>
       <c r="AE136" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF136" t="inlineStr">
@@ -16033,7 +16033,7 @@
       </c>
       <c r="AE137" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:47</t>
+          <t>2026-10-06 15:24:28</t>
         </is>
       </c>
       <c r="AF137" t="inlineStr">
@@ -16145,7 +16145,7 @@
       </c>
       <c r="AE138" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF138" t="inlineStr">
@@ -16261,7 +16261,7 @@
       </c>
       <c r="AE139" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF139" t="inlineStr">
@@ -16383,7 +16383,7 @@
       <c r="AD140" t="inlineStr"/>
       <c r="AE140" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF140" t="inlineStr">
@@ -16495,7 +16495,7 @@
       </c>
       <c r="AE141" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:49</t>
+          <t>2026-10-06 15:24:30</t>
         </is>
       </c>
       <c r="AF141" t="inlineStr">
@@ -16623,7 +16623,7 @@
       </c>
       <c r="AE142" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF142" t="inlineStr">
@@ -16743,7 +16743,7 @@
       </c>
       <c r="AE143" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF143" t="inlineStr">
@@ -16863,7 +16863,7 @@
       </c>
       <c r="AE144" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF144" t="inlineStr">
@@ -16973,7 +16973,7 @@
       </c>
       <c r="AE145" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF145" t="inlineStr">
@@ -17089,7 +17089,7 @@
       </c>
       <c r="AE146" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF146" t="inlineStr">
@@ -17201,7 +17201,7 @@
       </c>
       <c r="AE147" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF147" t="inlineStr">
@@ -17311,7 +17311,7 @@
       </c>
       <c r="AE148" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF148" t="inlineStr">
@@ -17421,7 +17421,7 @@
       </c>
       <c r="AE149" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF149" t="inlineStr">
@@ -17537,7 +17537,7 @@
       </c>
       <c r="AE150" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF150" t="inlineStr">
@@ -17649,7 +17649,7 @@
       </c>
       <c r="AE151" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF151" t="inlineStr">
@@ -17769,7 +17769,7 @@
       </c>
       <c r="AE152" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF152" t="inlineStr">
@@ -17881,7 +17881,7 @@
       </c>
       <c r="AE153" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF153" t="inlineStr">
@@ -17997,7 +17997,7 @@
       </c>
       <c r="AE154" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF154" t="inlineStr">
@@ -18107,7 +18107,7 @@
       </c>
       <c r="AE155" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF155" t="inlineStr">
@@ -18217,7 +18217,7 @@
       </c>
       <c r="AE156" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF156" t="inlineStr">
@@ -18337,7 +18337,7 @@
       </c>
       <c r="AE157" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF157" t="inlineStr">
@@ -18451,7 +18451,7 @@
       </c>
       <c r="AE158" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF158" t="inlineStr">
@@ -18565,7 +18565,7 @@
       </c>
       <c r="AE159" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF159" t="inlineStr">
@@ -18685,7 +18685,7 @@
       </c>
       <c r="AE160" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF160" t="inlineStr">
@@ -18795,7 +18795,7 @@
       </c>
       <c r="AE161" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF161" t="inlineStr">
@@ -18911,7 +18911,7 @@
       </c>
       <c r="AE162" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF162" t="inlineStr">
@@ -19023,7 +19023,7 @@
       </c>
       <c r="AE163" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:49</t>
+          <t>2026-10-06 15:24:30</t>
         </is>
       </c>
       <c r="AF163" t="inlineStr">
@@ -19135,7 +19135,7 @@
       </c>
       <c r="AE164" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF164" t="inlineStr">
@@ -19249,7 +19249,7 @@
       </c>
       <c r="AE165" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF165" t="inlineStr">
@@ -19363,7 +19363,7 @@
       </c>
       <c r="AE166" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF166" t="inlineStr">
@@ -19477,7 +19477,7 @@
       </c>
       <c r="AE167" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:47</t>
+          <t>2026-10-06 15:24:28</t>
         </is>
       </c>
       <c r="AF167" t="inlineStr">
@@ -19587,7 +19587,7 @@
       </c>
       <c r="AE168" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF168" t="inlineStr">
@@ -19697,7 +19697,7 @@
       </c>
       <c r="AE169" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF169" t="inlineStr">
@@ -19807,7 +19807,7 @@
       </c>
       <c r="AE170" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF170" t="inlineStr">
@@ -19921,7 +19921,7 @@
       </c>
       <c r="AE171" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF171" t="inlineStr">
@@ -20035,7 +20035,7 @@
       </c>
       <c r="AE172" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF172" t="inlineStr">
@@ -20163,7 +20163,7 @@
       </c>
       <c r="AE173" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF173" t="inlineStr">
@@ -20291,7 +20291,7 @@
       </c>
       <c r="AE174" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF174" t="inlineStr">
@@ -20401,7 +20401,7 @@
       </c>
       <c r="AE175" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF175" t="inlineStr">
@@ -20511,7 +20511,7 @@
       </c>
       <c r="AE176" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF176" t="inlineStr">
@@ -20631,7 +20631,7 @@
       </c>
       <c r="AE177" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF177" t="inlineStr">
@@ -20745,7 +20745,7 @@
       </c>
       <c r="AE178" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF178" t="inlineStr">
@@ -20855,7 +20855,7 @@
       </c>
       <c r="AE179" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF179" t="inlineStr">
@@ -20983,7 +20983,7 @@
       </c>
       <c r="AE180" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF180" t="inlineStr">
@@ -21105,7 +21105,7 @@
       <c r="AD181" t="inlineStr"/>
       <c r="AE181" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF181" t="inlineStr">
@@ -21233,7 +21233,7 @@
       </c>
       <c r="AE182" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF182" t="inlineStr">
@@ -21349,7 +21349,7 @@
       </c>
       <c r="AE183" t="inlineStr">
         <is>
-          <t>2026-10-06 10:43:02</t>
+          <t>2026-10-06 15:24:42</t>
         </is>
       </c>
       <c r="AF183" t="inlineStr">
@@ -21477,7 +21477,7 @@
       </c>
       <c r="AE184" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF184" t="inlineStr">
@@ -21609,7 +21609,7 @@
       </c>
       <c r="AE185" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF185" t="inlineStr">
@@ -21723,7 +21723,7 @@
       </c>
       <c r="AE186" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF186" t="inlineStr">
@@ -21845,7 +21845,7 @@
       <c r="AD187" t="inlineStr"/>
       <c r="AE187" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF187" t="inlineStr">
@@ -21957,7 +21957,7 @@
       </c>
       <c r="AE188" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF188" t="inlineStr">
@@ -22057,7 +22057,7 @@
       </c>
       <c r="AE189" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF189" t="inlineStr">
@@ -22167,7 +22167,7 @@
       </c>
       <c r="AE190" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF190" t="inlineStr">
@@ -22283,7 +22283,7 @@
       </c>
       <c r="AE191" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF191" t="inlineStr">
@@ -22399,7 +22399,7 @@
       </c>
       <c r="AE192" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF192" t="inlineStr">
@@ -22527,7 +22527,7 @@
       </c>
       <c r="AE193" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF193" t="inlineStr">
@@ -22637,7 +22637,7 @@
       </c>
       <c r="AE194" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF194" t="inlineStr">
@@ -22751,7 +22751,7 @@
       </c>
       <c r="AE195" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF195" t="inlineStr">
@@ -22865,7 +22865,7 @@
       </c>
       <c r="AE196" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF196" t="inlineStr">
@@ -22979,7 +22979,7 @@
       </c>
       <c r="AE197" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF197" t="inlineStr">
@@ -23089,7 +23089,7 @@
       </c>
       <c r="AE198" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF198" t="inlineStr">
@@ -23203,7 +23203,7 @@
       </c>
       <c r="AE199" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF199" t="inlineStr">
@@ -23313,7 +23313,7 @@
       </c>
       <c r="AE200" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF200" t="inlineStr">
@@ -23425,7 +23425,7 @@
       </c>
       <c r="AE201" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF201" t="inlineStr">
@@ -23541,7 +23541,7 @@
       </c>
       <c r="AE202" t="inlineStr">
         <is>
-          <t>2026-10-06 10:43:02</t>
+          <t>2026-10-06 15:24:42</t>
         </is>
       </c>
       <c r="AF202" t="inlineStr">
@@ -23657,7 +23657,7 @@
       </c>
       <c r="AE203" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF203" t="inlineStr">
@@ -23769,7 +23769,7 @@
       </c>
       <c r="AE204" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF204" t="inlineStr">
@@ -23881,7 +23881,7 @@
       </c>
       <c r="AE205" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF205" t="inlineStr">
@@ -23993,7 +23993,7 @@
       </c>
       <c r="AE206" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF206" t="inlineStr">
@@ -24121,7 +24121,7 @@
       </c>
       <c r="AE207" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:49</t>
+          <t>2026-10-06 15:24:30</t>
         </is>
       </c>
       <c r="AF207" t="inlineStr">
@@ -24231,7 +24231,7 @@
       </c>
       <c r="AE208" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF208" t="inlineStr">
@@ -24351,7 +24351,7 @@
       </c>
       <c r="AE209" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF209" t="inlineStr">
@@ -24473,7 +24473,7 @@
       <c r="AD210" t="inlineStr"/>
       <c r="AE210" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF210" t="inlineStr">
@@ -24599,7 +24599,7 @@
       <c r="AD211" t="inlineStr"/>
       <c r="AE211" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF211" t="inlineStr">
@@ -24725,7 +24725,7 @@
       <c r="AD212" t="inlineStr"/>
       <c r="AE212" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF212" t="inlineStr">
@@ -24841,7 +24841,7 @@
       </c>
       <c r="AE213" t="inlineStr">
         <is>
-          <t>2026-10-06 10:43:02</t>
+          <t>2026-10-06 15:24:42</t>
         </is>
       </c>
       <c r="AF213" t="inlineStr">
@@ -24955,7 +24955,7 @@
       </c>
       <c r="AE214" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF214" t="inlineStr">
@@ -25069,7 +25069,7 @@
       </c>
       <c r="AE215" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF215" t="inlineStr">
@@ -25183,7 +25183,7 @@
       </c>
       <c r="AE216" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF216" t="inlineStr">
@@ -25303,7 +25303,7 @@
       </c>
       <c r="AE217" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF217" t="inlineStr">
@@ -25423,7 +25423,7 @@
       </c>
       <c r="AE218" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF218" t="inlineStr">
@@ -25533,7 +25533,7 @@
       </c>
       <c r="AE219" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF219" t="inlineStr">
@@ -25643,7 +25643,7 @@
       </c>
       <c r="AE220" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF220" t="inlineStr">
@@ -25753,7 +25753,7 @@
       </c>
       <c r="AE221" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF221" t="inlineStr">
@@ -25869,7 +25869,7 @@
       </c>
       <c r="AE222" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF222" t="inlineStr">
@@ -25997,7 +25997,7 @@
       </c>
       <c r="AE223" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF223" t="inlineStr">
@@ -26109,7 +26109,7 @@
       </c>
       <c r="AE224" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF224" t="inlineStr">
@@ -26221,7 +26221,7 @@
       </c>
       <c r="AE225" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF225" t="inlineStr">
@@ -26339,7 +26339,7 @@
       </c>
       <c r="AE226" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:47</t>
+          <t>2026-10-06 15:24:28</t>
         </is>
       </c>
       <c r="AF226" t="inlineStr">
@@ -26449,7 +26449,7 @@
       </c>
       <c r="AE227" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF227" t="inlineStr">
@@ -26559,7 +26559,7 @@
       </c>
       <c r="AE228" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF228" t="inlineStr">
@@ -26671,7 +26671,7 @@
       </c>
       <c r="AE229" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF229" t="inlineStr">
@@ -26781,7 +26781,7 @@
       </c>
       <c r="AE230" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF230" t="inlineStr">
@@ -26901,7 +26901,7 @@
       </c>
       <c r="AE231" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF231" t="inlineStr">
@@ -27017,7 +27017,7 @@
       </c>
       <c r="AE232" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF232" t="inlineStr">
@@ -27133,7 +27133,7 @@
       </c>
       <c r="AE233" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF233" t="inlineStr">
@@ -27261,7 +27261,7 @@
       </c>
       <c r="AE234" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF234" t="inlineStr">
@@ -27373,7 +27373,7 @@
       </c>
       <c r="AE235" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF235" t="inlineStr">
@@ -27485,7 +27485,7 @@
       </c>
       <c r="AE236" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF236" t="inlineStr">
@@ -27597,7 +27597,7 @@
       </c>
       <c r="AE237" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF237" t="inlineStr">
@@ -27713,7 +27713,7 @@
       </c>
       <c r="AE238" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF238" t="inlineStr">
@@ -27823,7 +27823,7 @@
       </c>
       <c r="AE239" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF239" t="inlineStr">
@@ -27943,7 +27943,7 @@
       </c>
       <c r="AE240" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF240" t="inlineStr">
@@ -28053,7 +28053,7 @@
       </c>
       <c r="AE241" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF241" t="inlineStr">
@@ -28173,7 +28173,7 @@
       </c>
       <c r="AE242" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF242" t="inlineStr">
@@ -28283,7 +28283,7 @@
       </c>
       <c r="AE243" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF243" t="inlineStr">
@@ -28397,7 +28397,7 @@
       </c>
       <c r="AE244" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:47</t>
+          <t>2026-10-06 15:24:28</t>
         </is>
       </c>
       <c r="AF244" t="inlineStr">
@@ -28507,7 +28507,7 @@
       </c>
       <c r="AE245" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF245" t="inlineStr">
@@ -28617,7 +28617,7 @@
       </c>
       <c r="AE246" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF246" t="inlineStr">
@@ -28731,7 +28731,7 @@
       </c>
       <c r="AE247" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF247" t="inlineStr">
@@ -28841,7 +28841,7 @@
       </c>
       <c r="AE248" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF248" t="inlineStr">
@@ -28953,7 +28953,7 @@
       </c>
       <c r="AE249" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF249" t="inlineStr">
@@ -29063,7 +29063,7 @@
       </c>
       <c r="AE250" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF250" t="inlineStr">
@@ -29183,7 +29183,7 @@
       </c>
       <c r="AE251" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF251" t="inlineStr">
@@ -29295,7 +29295,7 @@
       </c>
       <c r="AE252" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF252" t="inlineStr">
@@ -29405,7 +29405,7 @@
       </c>
       <c r="AE253" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF253" t="inlineStr">
@@ -29529,7 +29529,7 @@
       </c>
       <c r="AE254" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:49</t>
+          <t>2026-10-06 15:24:30</t>
         </is>
       </c>
       <c r="AF254" t="inlineStr">
@@ -29653,7 +29653,7 @@
       </c>
       <c r="AE255" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:49</t>
+          <t>2026-10-06 15:24:30</t>
         </is>
       </c>
       <c r="AF255" t="inlineStr">
@@ -29763,7 +29763,7 @@
       </c>
       <c r="AE256" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF256" t="inlineStr">
@@ -29873,7 +29873,7 @@
       </c>
       <c r="AE257" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF257" t="inlineStr">
@@ -29983,7 +29983,7 @@
       </c>
       <c r="AE258" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF258" t="inlineStr">
@@ -30095,7 +30095,7 @@
       </c>
       <c r="AE259" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF259" t="inlineStr">
@@ -30205,7 +30205,7 @@
       </c>
       <c r="AE260" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF260" t="inlineStr">
@@ -30315,7 +30315,7 @@
       </c>
       <c r="AE261" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF261" t="inlineStr">
@@ -30443,7 +30443,7 @@
       </c>
       <c r="AE262" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF262" t="inlineStr">
@@ -30549,7 +30549,7 @@
       </c>
       <c r="AE263" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF263" t="inlineStr">
@@ -30661,7 +30661,7 @@
       </c>
       <c r="AE264" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF264" t="inlineStr">
@@ -30777,7 +30777,7 @@
       </c>
       <c r="AE265" t="inlineStr">
         <is>
-          <t>2026-10-06 10:43:02</t>
+          <t>2026-10-06 15:24:42</t>
         </is>
       </c>
       <c r="AF265" t="inlineStr">
@@ -30893,7 +30893,7 @@
       </c>
       <c r="AE266" t="inlineStr">
         <is>
-          <t>2026-10-06 10:43:02</t>
+          <t>2026-10-06 15:24:42</t>
         </is>
       </c>
       <c r="AF266" t="inlineStr">
@@ -31003,7 +31003,7 @@
       </c>
       <c r="AE267" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF267" t="inlineStr">
@@ -31113,7 +31113,7 @@
       </c>
       <c r="AE268" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF268" t="inlineStr">
@@ -31229,7 +31229,7 @@
       </c>
       <c r="AE269" t="inlineStr">
         <is>
-          <t>2026-10-06 10:43:02</t>
+          <t>2026-10-06 15:24:42</t>
         </is>
       </c>
       <c r="AF269" t="inlineStr">
@@ -31345,7 +31345,7 @@
       </c>
       <c r="AE270" t="inlineStr">
         <is>
-          <t>2026-10-06 10:43:02</t>
+          <t>2026-10-06 15:24:42</t>
         </is>
       </c>
       <c r="AF270" t="inlineStr">
@@ -31455,7 +31455,7 @@
       </c>
       <c r="AE271" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF271" t="inlineStr">
@@ -31571,7 +31571,7 @@
       </c>
       <c r="AE272" t="inlineStr">
         <is>
-          <t>2026-10-06 10:43:02</t>
+          <t>2026-10-06 15:24:42</t>
         </is>
       </c>
       <c r="AF272" t="inlineStr">
@@ -31687,7 +31687,7 @@
       </c>
       <c r="AE273" t="inlineStr">
         <is>
-          <t>2026-10-06 10:43:02</t>
+          <t>2026-10-06 15:24:42</t>
         </is>
       </c>
       <c r="AF273" t="inlineStr">
@@ -31797,7 +31797,7 @@
       </c>
       <c r="AE274" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF274" t="inlineStr">
@@ -31907,7 +31907,7 @@
       </c>
       <c r="AE275" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF275" t="inlineStr">
@@ -32017,7 +32017,7 @@
       </c>
       <c r="AE276" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF276" t="inlineStr">
@@ -32117,7 +32117,7 @@
       </c>
       <c r="AE277" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF277" t="inlineStr">
@@ -32227,7 +32227,7 @@
       </c>
       <c r="AE278" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF278" t="inlineStr">
@@ -32339,7 +32339,7 @@
       </c>
       <c r="AE279" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF279" t="inlineStr">
@@ -32449,7 +32449,7 @@
       </c>
       <c r="AE280" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF280" t="inlineStr">
@@ -32569,7 +32569,7 @@
       </c>
       <c r="AE281" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF281" t="inlineStr">
@@ -32681,7 +32681,7 @@
       </c>
       <c r="AE282" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF282" t="inlineStr">
@@ -32791,7 +32791,7 @@
       </c>
       <c r="AE283" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF283" t="inlineStr">
@@ -32903,7 +32903,7 @@
       </c>
       <c r="AE284" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF284" t="inlineStr">
@@ -33019,7 +33019,7 @@
       </c>
       <c r="AE285" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF285" t="inlineStr">
@@ -33131,7 +33131,7 @@
       </c>
       <c r="AE286" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF286" t="inlineStr">
@@ -33241,7 +33241,7 @@
       </c>
       <c r="AE287" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF287" t="inlineStr">
@@ -33357,7 +33357,7 @@
       </c>
       <c r="AE288" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF288" t="inlineStr">
@@ -33467,7 +33467,7 @@
       </c>
       <c r="AE289" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF289" t="inlineStr">
@@ -33593,7 +33593,7 @@
       <c r="AD290" t="inlineStr"/>
       <c r="AE290" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF290" t="inlineStr">
@@ -33721,7 +33721,7 @@
       </c>
       <c r="AE291" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF291" t="inlineStr">
@@ -33833,7 +33833,7 @@
       </c>
       <c r="AE292" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF292" t="inlineStr">
@@ -33933,7 +33933,7 @@
       </c>
       <c r="AE293" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF293" t="inlineStr">
@@ -34033,7 +34033,7 @@
       </c>
       <c r="AE294" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF294" t="inlineStr">
@@ -34147,7 +34147,7 @@
       </c>
       <c r="AE295" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF295" t="inlineStr">
@@ -34261,7 +34261,7 @@
       </c>
       <c r="AE296" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF296" t="inlineStr">
@@ -34361,7 +34361,7 @@
       </c>
       <c r="AE297" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF297" t="inlineStr">
@@ -34481,7 +34481,7 @@
       </c>
       <c r="AE298" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF298" t="inlineStr">
@@ -34593,7 +34593,7 @@
       </c>
       <c r="AE299" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF299" t="inlineStr">
@@ -34705,7 +34705,7 @@
       </c>
       <c r="AE300" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF300" t="inlineStr">
@@ -34819,7 +34819,7 @@
       </c>
       <c r="AE301" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF301" t="inlineStr">
@@ -34933,7 +34933,7 @@
       </c>
       <c r="AE302" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:47</t>
+          <t>2026-10-06 15:24:28</t>
         </is>
       </c>
       <c r="AF302" t="inlineStr">
@@ -35047,7 +35047,7 @@
       </c>
       <c r="AE303" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:47</t>
+          <t>2026-10-06 15:24:28</t>
         </is>
       </c>
       <c r="AF303" t="inlineStr">
@@ -35179,7 +35179,7 @@
       </c>
       <c r="AE304" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF304" t="inlineStr">
@@ -35307,7 +35307,7 @@
       </c>
       <c r="AE305" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF305" t="inlineStr">
@@ -35435,7 +35435,7 @@
       </c>
       <c r="AE306" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF306" t="inlineStr">
@@ -35563,7 +35563,7 @@
       </c>
       <c r="AE307" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF307" t="inlineStr">
@@ -35675,7 +35675,7 @@
       </c>
       <c r="AE308" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF308" t="inlineStr">
@@ -35787,7 +35787,7 @@
       </c>
       <c r="AE309" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF309" t="inlineStr">
@@ -35897,7 +35897,7 @@
       </c>
       <c r="AE310" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF310" t="inlineStr">
@@ -36007,7 +36007,7 @@
       </c>
       <c r="AE311" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF311" t="inlineStr">
@@ -36135,7 +36135,7 @@
       </c>
       <c r="AE312" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF312" t="inlineStr">
@@ -36245,7 +36245,7 @@
       </c>
       <c r="AE313" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF313" t="inlineStr">
@@ -36373,7 +36373,7 @@
       </c>
       <c r="AE314" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF314" t="inlineStr">
@@ -36485,7 +36485,7 @@
       </c>
       <c r="AE315" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF315" t="inlineStr">
@@ -36597,7 +36597,7 @@
       </c>
       <c r="AE316" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF316" t="inlineStr">
@@ -36707,7 +36707,7 @@
       </c>
       <c r="AE317" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF317" t="inlineStr">
@@ -36827,7 +36827,7 @@
       </c>
       <c r="AE318" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF318" t="inlineStr">
@@ -36951,7 +36951,7 @@
       </c>
       <c r="AE319" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF319" t="inlineStr">
@@ -37075,7 +37075,7 @@
       </c>
       <c r="AE320" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF320" t="inlineStr">
@@ -37199,7 +37199,7 @@
       </c>
       <c r="AE321" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF321" t="inlineStr">
@@ -37311,7 +37311,7 @@
       </c>
       <c r="AE322" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF322" t="inlineStr">
@@ -37427,7 +37427,7 @@
       </c>
       <c r="AE323" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF323" t="inlineStr">
@@ -37539,7 +37539,7 @@
       </c>
       <c r="AE324" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:49</t>
+          <t>2026-10-06 15:24:30</t>
         </is>
       </c>
       <c r="AF324" t="inlineStr">
@@ -37667,7 +37667,7 @@
       </c>
       <c r="AE325" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:49</t>
+          <t>2026-10-06 15:24:30</t>
         </is>
       </c>
       <c r="AF325" t="inlineStr">
@@ -37795,7 +37795,7 @@
       </c>
       <c r="AE326" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF326" t="inlineStr">
@@ -37907,7 +37907,7 @@
       </c>
       <c r="AE327" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF327" t="inlineStr">
@@ -38019,7 +38019,7 @@
       </c>
       <c r="AE328" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF328" t="inlineStr">
@@ -38129,7 +38129,7 @@
       </c>
       <c r="AE329" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF329" t="inlineStr">
@@ -38239,7 +38239,7 @@
       </c>
       <c r="AE330" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF330" t="inlineStr">
@@ -38355,7 +38355,7 @@
       </c>
       <c r="AE331" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF331" t="inlineStr">
@@ -38467,7 +38467,7 @@
       </c>
       <c r="AE332" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF332" t="inlineStr">
@@ -38587,7 +38587,7 @@
       </c>
       <c r="AE333" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF333" t="inlineStr">
@@ -38715,7 +38715,7 @@
       </c>
       <c r="AE334" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF334" t="inlineStr">
@@ -38831,7 +38831,7 @@
       </c>
       <c r="AE335" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF335" t="inlineStr">
@@ -38931,7 +38931,7 @@
       </c>
       <c r="AE336" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF336" t="inlineStr">
@@ -39043,7 +39043,7 @@
       </c>
       <c r="AE337" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF337" t="inlineStr">
@@ -39171,7 +39171,7 @@
       </c>
       <c r="AE338" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF338" t="inlineStr">
@@ -39295,7 +39295,7 @@
       </c>
       <c r="AE339" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:49</t>
+          <t>2026-10-06 15:24:30</t>
         </is>
       </c>
       <c r="AF339" t="inlineStr">
@@ -39407,7 +39407,7 @@
       </c>
       <c r="AE340" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF340" t="inlineStr">
@@ -39517,7 +39517,7 @@
       </c>
       <c r="AE341" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF341" t="inlineStr">
@@ -39627,7 +39627,7 @@
       </c>
       <c r="AE342" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF342" t="inlineStr">
@@ -39737,7 +39737,7 @@
       </c>
       <c r="AE343" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF343" t="inlineStr">
@@ -39847,7 +39847,7 @@
       </c>
       <c r="AE344" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF344" t="inlineStr">
@@ -39967,7 +39967,7 @@
       </c>
       <c r="AE345" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF345" t="inlineStr">
@@ -40077,7 +40077,7 @@
       </c>
       <c r="AE346" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF346" t="inlineStr">
@@ -40187,7 +40187,7 @@
       </c>
       <c r="AE347" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF347" t="inlineStr">
@@ -40297,7 +40297,7 @@
       </c>
       <c r="AE348" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF348" t="inlineStr">
@@ -40417,7 +40417,7 @@
       </c>
       <c r="AE349" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF349" t="inlineStr">
@@ -40537,7 +40537,7 @@
       </c>
       <c r="AE350" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF350" t="inlineStr">
@@ -40657,7 +40657,7 @@
       </c>
       <c r="AE351" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF351" t="inlineStr">
@@ -40777,7 +40777,7 @@
       </c>
       <c r="AE352" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF352" t="inlineStr">
@@ -40893,7 +40893,7 @@
       </c>
       <c r="AE353" t="inlineStr">
         <is>
-          <t>2026-10-06 10:43:02</t>
+          <t>2026-10-06 15:24:42</t>
         </is>
       </c>
       <c r="AF353" t="inlineStr">
@@ -41009,7 +41009,7 @@
       </c>
       <c r="AE354" t="inlineStr">
         <is>
-          <t>2026-10-06 10:43:02</t>
+          <t>2026-10-06 15:24:42</t>
         </is>
       </c>
       <c r="AF354" t="inlineStr">
@@ -41125,7 +41125,7 @@
       </c>
       <c r="AE355" t="inlineStr">
         <is>
-          <t>2026-10-06 10:43:02</t>
+          <t>2026-10-06 15:24:42</t>
         </is>
       </c>
       <c r="AF355" t="inlineStr">
@@ -41237,7 +41237,7 @@
       </c>
       <c r="AE356" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF356" t="inlineStr">
@@ -41353,7 +41353,7 @@
       </c>
       <c r="AE357" t="inlineStr">
         <is>
-          <t>2026-10-06 10:43:02</t>
+          <t>2026-10-06 15:24:42</t>
         </is>
       </c>
       <c r="AF357" t="inlineStr">
@@ -41473,7 +41473,7 @@
       </c>
       <c r="AE358" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF358" t="inlineStr">
@@ -41585,7 +41585,7 @@
       </c>
       <c r="AE359" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF359" t="inlineStr">
@@ -41701,7 +41701,7 @@
       </c>
       <c r="AE360" t="inlineStr">
         <is>
-          <t>2026-10-06 10:43:02</t>
+          <t>2026-10-06 15:24:42</t>
         </is>
       </c>
       <c r="AF360" t="inlineStr">
@@ -41817,7 +41817,7 @@
       </c>
       <c r="AE361" t="inlineStr">
         <is>
-          <t>2026-10-06 10:43:02</t>
+          <t>2026-10-06 15:24:42</t>
         </is>
       </c>
       <c r="AF361" t="inlineStr">
@@ -41933,7 +41933,7 @@
       </c>
       <c r="AE362" t="inlineStr">
         <is>
-          <t>2026-10-06 10:43:02</t>
+          <t>2026-10-06 15:24:42</t>
         </is>
       </c>
       <c r="AF362" t="inlineStr">
@@ -42049,7 +42049,7 @@
       </c>
       <c r="AE363" t="inlineStr">
         <is>
-          <t>2026-10-06 10:43:02</t>
+          <t>2026-10-06 15:24:42</t>
         </is>
       </c>
       <c r="AF363" t="inlineStr">
@@ -42163,7 +42163,7 @@
       </c>
       <c r="AE364" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:47</t>
+          <t>2026-10-06 15:24:28</t>
         </is>
       </c>
       <c r="AF364" t="inlineStr">
@@ -42279,7 +42279,7 @@
       </c>
       <c r="AE365" t="inlineStr">
         <is>
-          <t>2026-10-06 10:43:02</t>
+          <t>2026-10-06 15:24:42</t>
         </is>
       </c>
       <c r="AF365" t="inlineStr">
@@ -42395,7 +42395,7 @@
       </c>
       <c r="AE366" t="inlineStr">
         <is>
-          <t>2026-10-06 10:43:02</t>
+          <t>2026-10-06 15:24:42</t>
         </is>
       </c>
       <c r="AF366" t="inlineStr">
@@ -42511,7 +42511,7 @@
       </c>
       <c r="AE367" t="inlineStr">
         <is>
-          <t>2026-10-06 10:43:02</t>
+          <t>2026-10-06 15:24:42</t>
         </is>
       </c>
       <c r="AF367" t="inlineStr">
@@ -42621,7 +42621,7 @@
       </c>
       <c r="AE368" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF368" t="inlineStr">
@@ -42737,7 +42737,7 @@
       </c>
       <c r="AE369" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF369" t="inlineStr">
@@ -42849,7 +42849,7 @@
       </c>
       <c r="AE370" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF370" t="inlineStr">
@@ -42959,7 +42959,7 @@
       </c>
       <c r="AE371" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF371" t="inlineStr">
@@ -43071,7 +43071,7 @@
       </c>
       <c r="AE372" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF372" t="inlineStr">
@@ -43183,7 +43183,7 @@
       </c>
       <c r="AE373" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF373" t="inlineStr">
@@ -43295,7 +43295,7 @@
       </c>
       <c r="AE374" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF374" t="inlineStr">
@@ -43415,7 +43415,7 @@
       </c>
       <c r="AE375" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF375" t="inlineStr">
@@ -43543,7 +43543,7 @@
       </c>
       <c r="AE376" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF376" t="inlineStr">
@@ -43663,7 +43663,7 @@
       </c>
       <c r="AE377" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF377" t="inlineStr">
@@ -43791,7 +43791,7 @@
       </c>
       <c r="AE378" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF378" t="inlineStr">
@@ -43903,7 +43903,7 @@
       </c>
       <c r="AE379" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF379" t="inlineStr">
@@ -44013,7 +44013,7 @@
       </c>
       <c r="AE380" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF380" t="inlineStr">
@@ -44123,7 +44123,7 @@
       </c>
       <c r="AE381" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF381" t="inlineStr">
@@ -44235,7 +44235,7 @@
       </c>
       <c r="AE382" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF382" t="inlineStr">
@@ -44347,7 +44347,7 @@
       </c>
       <c r="AE383" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF383" t="inlineStr">
@@ -44457,7 +44457,7 @@
       </c>
       <c r="AE384" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF384" t="inlineStr">
@@ -44573,7 +44573,7 @@
       </c>
       <c r="AE385" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF385" t="inlineStr">
@@ -44683,7 +44683,7 @@
       </c>
       <c r="AE386" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF386" t="inlineStr">
@@ -44795,7 +44795,7 @@
       </c>
       <c r="AE387" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF387" t="inlineStr">
@@ -44905,7 +44905,7 @@
       </c>
       <c r="AE388" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF388" t="inlineStr">
@@ -45015,7 +45015,7 @@
       </c>
       <c r="AE389" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF389" t="inlineStr">
@@ -45143,7 +45143,7 @@
       </c>
       <c r="AE390" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF390" t="inlineStr">
@@ -45255,7 +45255,7 @@
       </c>
       <c r="AE391" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF391" t="inlineStr">
@@ -45383,7 +45383,7 @@
       </c>
       <c r="AE392" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF392" t="inlineStr">
@@ -45495,7 +45495,7 @@
       </c>
       <c r="AE393" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF393" t="inlineStr">
@@ -45605,7 +45605,7 @@
       </c>
       <c r="AE394" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF394" t="inlineStr">
@@ -45715,7 +45715,7 @@
       </c>
       <c r="AE395" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF395" t="inlineStr">
@@ -45825,7 +45825,7 @@
       </c>
       <c r="AE396" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF396" t="inlineStr">
@@ -45937,7 +45937,7 @@
       </c>
       <c r="AE397" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF397" t="inlineStr">
@@ -46047,7 +46047,7 @@
       </c>
       <c r="AE398" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF398" t="inlineStr">
@@ -46175,7 +46175,7 @@
       </c>
       <c r="AE399" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF399" t="inlineStr">
@@ -46287,7 +46287,7 @@
       </c>
       <c r="AE400" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF400" t="inlineStr">
@@ -46397,7 +46397,7 @@
       </c>
       <c r="AE401" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF401" t="inlineStr">
@@ -46507,7 +46507,7 @@
       </c>
       <c r="AE402" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF402" t="inlineStr">
@@ -46617,7 +46617,7 @@
       </c>
       <c r="AE403" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF403" t="inlineStr">
@@ -46727,7 +46727,7 @@
       </c>
       <c r="AE404" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF404" t="inlineStr">
@@ -46837,7 +46837,7 @@
       </c>
       <c r="AE405" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF405" t="inlineStr">
@@ -46949,7 +46949,7 @@
       </c>
       <c r="AE406" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF406" t="inlineStr">
@@ -47077,7 +47077,7 @@
       </c>
       <c r="AE407" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF407" t="inlineStr">
@@ -47187,7 +47187,7 @@
       </c>
       <c r="AE408" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF408" t="inlineStr">
@@ -47297,7 +47297,7 @@
       </c>
       <c r="AE409" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF409" t="inlineStr">
@@ -47409,7 +47409,7 @@
       </c>
       <c r="AE410" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:49</t>
+          <t>2026-10-06 15:24:30</t>
         </is>
       </c>
       <c r="AF410" t="inlineStr">
@@ -47519,7 +47519,7 @@
       </c>
       <c r="AE411" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF411" t="inlineStr">
@@ -47631,7 +47631,7 @@
       </c>
       <c r="AE412" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF412" t="inlineStr">
@@ -47759,7 +47759,7 @@
       </c>
       <c r="AE413" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF413" t="inlineStr">
@@ -47869,7 +47869,7 @@
       </c>
       <c r="AE414" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF414" t="inlineStr">
@@ -47981,7 +47981,7 @@
       </c>
       <c r="AE415" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF415" t="inlineStr">
@@ -48091,7 +48091,7 @@
       </c>
       <c r="AE416" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF416" t="inlineStr">
@@ -48201,7 +48201,7 @@
       </c>
       <c r="AE417" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF417" t="inlineStr">
@@ -48311,7 +48311,7 @@
       </c>
       <c r="AE418" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF418" t="inlineStr">
@@ -48411,7 +48411,7 @@
       </c>
       <c r="AE419" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF419" t="inlineStr">
@@ -48521,7 +48521,7 @@
       </c>
       <c r="AE420" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF420" t="inlineStr">
@@ -48621,7 +48621,7 @@
       </c>
       <c r="AE421" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF421" t="inlineStr">
@@ -48731,7 +48731,7 @@
       </c>
       <c r="AE422" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF422" t="inlineStr">
@@ -48859,7 +48859,7 @@
       </c>
       <c r="AE423" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF423" t="inlineStr">
@@ -48969,7 +48969,7 @@
       </c>
       <c r="AE424" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF424" t="inlineStr">
@@ -49079,7 +49079,7 @@
       </c>
       <c r="AE425" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF425" t="inlineStr">
@@ -49189,7 +49189,7 @@
       </c>
       <c r="AE426" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF426" t="inlineStr">
@@ -49299,7 +49299,7 @@
       </c>
       <c r="AE427" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF427" t="inlineStr">
@@ -49409,7 +49409,7 @@
       </c>
       <c r="AE428" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF428" t="inlineStr">
@@ -49519,7 +49519,7 @@
       </c>
       <c r="AE429" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF429" t="inlineStr">
@@ -49629,7 +49629,7 @@
       </c>
       <c r="AE430" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF430" t="inlineStr">
@@ -49739,7 +49739,7 @@
       </c>
       <c r="AE431" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF431" t="inlineStr">
@@ -49867,7 +49867,7 @@
       </c>
       <c r="AE432" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF432" t="inlineStr">
@@ -49979,7 +49979,7 @@
       </c>
       <c r="AE433" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF433" t="inlineStr">
@@ -50079,7 +50079,7 @@
       </c>
       <c r="AE434" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF434" t="inlineStr">
@@ -50189,7 +50189,7 @@
       </c>
       <c r="AE435" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF435" t="inlineStr">
@@ -50303,7 +50303,7 @@
       </c>
       <c r="AE436" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF436" t="inlineStr">
@@ -50413,7 +50413,7 @@
       </c>
       <c r="AE437" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF437" t="inlineStr">
@@ -50513,7 +50513,7 @@
       </c>
       <c r="AE438" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF438" t="inlineStr">
@@ -50625,7 +50625,7 @@
       </c>
       <c r="AE439" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF439" t="inlineStr">
@@ -50737,7 +50737,7 @@
       </c>
       <c r="AE440" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF440" t="inlineStr">
@@ -50847,7 +50847,7 @@
       </c>
       <c r="AE441" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF441" t="inlineStr">
@@ -50959,7 +50959,7 @@
       </c>
       <c r="AE442" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF442" t="inlineStr">
@@ -51071,7 +51071,7 @@
       </c>
       <c r="AE443" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF443" t="inlineStr">
@@ -51181,7 +51181,7 @@
       </c>
       <c r="AE444" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF444" t="inlineStr">
@@ -51309,7 +51309,7 @@
       </c>
       <c r="AE445" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF445" t="inlineStr">
@@ -51441,7 +51441,7 @@
       </c>
       <c r="AE446" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF446" t="inlineStr">
@@ -51573,7 +51573,7 @@
       </c>
       <c r="AE447" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF447" t="inlineStr">
@@ -51705,7 +51705,7 @@
       </c>
       <c r="AE448" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF448" t="inlineStr">
@@ -51829,7 +51829,7 @@
       </c>
       <c r="AE449" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:49</t>
+          <t>2026-10-06 15:24:30</t>
         </is>
       </c>
       <c r="AF449" t="inlineStr">
@@ -51941,7 +51941,7 @@
       </c>
       <c r="AE450" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF450" t="inlineStr">
@@ -52041,7 +52041,7 @@
       </c>
       <c r="AE451" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF451" t="inlineStr">
@@ -52161,7 +52161,7 @@
       </c>
       <c r="AE452" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF452" t="inlineStr">
@@ -52277,7 +52277,7 @@
       </c>
       <c r="AE453" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF453" t="inlineStr">
@@ -52389,7 +52389,7 @@
       </c>
       <c r="AE454" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF454" t="inlineStr">
@@ -52511,7 +52511,7 @@
       <c r="AD455" t="inlineStr"/>
       <c r="AE455" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF455" t="inlineStr">
@@ -52623,7 +52623,7 @@
       </c>
       <c r="AE456" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF456" t="inlineStr">
@@ -52733,7 +52733,7 @@
       </c>
       <c r="AE457" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF457" t="inlineStr">
@@ -52843,7 +52843,7 @@
       </c>
       <c r="AE458" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF458" t="inlineStr">
@@ -52953,7 +52953,7 @@
       </c>
       <c r="AE459" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF459" t="inlineStr">
@@ -53063,7 +53063,7 @@
       </c>
       <c r="AE460" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF460" t="inlineStr">
@@ -53191,7 +53191,7 @@
       </c>
       <c r="AE461" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF461" t="inlineStr">
@@ -53307,7 +53307,7 @@
       </c>
       <c r="AE462" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF462" t="inlineStr">
@@ -53417,7 +53417,7 @@
       </c>
       <c r="AE463" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF463" t="inlineStr">
@@ -53545,7 +53545,7 @@
       </c>
       <c r="AE464" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF464" t="inlineStr">
@@ -53673,7 +53673,7 @@
       </c>
       <c r="AE465" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF465" t="inlineStr">
@@ -53801,7 +53801,7 @@
       </c>
       <c r="AE466" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF466" t="inlineStr">
@@ -53929,7 +53929,7 @@
       </c>
       <c r="AE467" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF467" t="inlineStr">
@@ -54041,7 +54041,7 @@
       </c>
       <c r="AE468" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF468" t="inlineStr">
@@ -54151,7 +54151,7 @@
       </c>
       <c r="AE469" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF469" t="inlineStr">
@@ -54279,7 +54279,7 @@
       </c>
       <c r="AE470" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF470" t="inlineStr">
@@ -54391,7 +54391,7 @@
       </c>
       <c r="AE471" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF471" t="inlineStr">
@@ -54503,7 +54503,7 @@
       </c>
       <c r="AE472" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF472" t="inlineStr">
@@ -54619,7 +54619,7 @@
       </c>
       <c r="AE473" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF473" t="inlineStr">
@@ -54731,7 +54731,7 @@
       </c>
       <c r="AE474" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF474" t="inlineStr">
@@ -54843,7 +54843,7 @@
       </c>
       <c r="AE475" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF475" t="inlineStr">
@@ -54955,7 +54955,7 @@
       </c>
       <c r="AE476" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF476" t="inlineStr">
@@ -55067,7 +55067,7 @@
       </c>
       <c r="AE477" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF477" t="inlineStr">
@@ -55187,7 +55187,7 @@
       </c>
       <c r="AE478" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF478" t="inlineStr">
@@ -55297,7 +55297,7 @@
       </c>
       <c r="AE479" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF479" t="inlineStr">
@@ -55425,7 +55425,7 @@
       </c>
       <c r="AE480" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF480" t="inlineStr">
@@ -55545,7 +55545,7 @@
       </c>
       <c r="AE481" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF481" t="inlineStr">
@@ -55657,7 +55657,7 @@
       </c>
       <c r="AE482" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF482" t="inlineStr">
@@ -55769,7 +55769,7 @@
       </c>
       <c r="AE483" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF483" t="inlineStr">
@@ -55869,7 +55869,7 @@
       </c>
       <c r="AE484" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF484" t="inlineStr">
@@ -55985,7 +55985,7 @@
       </c>
       <c r="AE485" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF485" t="inlineStr">
@@ -56095,7 +56095,7 @@
       </c>
       <c r="AE486" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF486" t="inlineStr">
@@ -56207,7 +56207,7 @@
       </c>
       <c r="AE487" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF487" t="inlineStr">
@@ -56317,7 +56317,7 @@
       </c>
       <c r="AE488" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF488" t="inlineStr">
@@ -56429,7 +56429,7 @@
       </c>
       <c r="AE489" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF489" t="inlineStr">
@@ -56541,7 +56541,7 @@
       </c>
       <c r="AE490" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF490" t="inlineStr">
@@ -56641,7 +56641,7 @@
       </c>
       <c r="AE491" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF491" t="inlineStr">
@@ -56751,7 +56751,7 @@
       </c>
       <c r="AE492" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF492" t="inlineStr">
@@ -56863,7 +56863,7 @@
       </c>
       <c r="AE493" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF493" t="inlineStr">
@@ -56973,7 +56973,7 @@
       </c>
       <c r="AE494" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF494" t="inlineStr">
@@ -57083,7 +57083,7 @@
       </c>
       <c r="AE495" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF495" t="inlineStr">
@@ -57195,7 +57195,7 @@
       </c>
       <c r="AE496" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF496" t="inlineStr">
@@ -57305,7 +57305,7 @@
       </c>
       <c r="AE497" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF497" t="inlineStr">
@@ -57415,7 +57415,7 @@
       </c>
       <c r="AE498" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF498" t="inlineStr">
@@ -57525,7 +57525,7 @@
       </c>
       <c r="AE499" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF499" t="inlineStr">
@@ -57645,7 +57645,7 @@
       </c>
       <c r="AE500" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF500" t="inlineStr">
@@ -57769,7 +57769,7 @@
       </c>
       <c r="AE501" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:49</t>
+          <t>2026-10-06 15:24:30</t>
         </is>
       </c>
       <c r="AF501" t="inlineStr">
@@ -57879,7 +57879,7 @@
       </c>
       <c r="AE502" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF502" t="inlineStr">
@@ -57991,7 +57991,7 @@
       </c>
       <c r="AE503" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF503" t="inlineStr">
@@ -58101,7 +58101,7 @@
       </c>
       <c r="AE504" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF504" t="inlineStr">
@@ -58213,7 +58213,7 @@
       </c>
       <c r="AE505" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF505" t="inlineStr">
@@ -58325,7 +58325,7 @@
       </c>
       <c r="AE506" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF506" t="inlineStr">
@@ -58435,7 +58435,7 @@
       </c>
       <c r="AE507" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF507" t="inlineStr">
@@ -58545,7 +58545,7 @@
       </c>
       <c r="AE508" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF508" t="inlineStr">
@@ -58655,7 +58655,7 @@
       </c>
       <c r="AE509" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF509" t="inlineStr">
@@ -58765,7 +58765,7 @@
       </c>
       <c r="AE510" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF510" t="inlineStr">
@@ -58875,7 +58875,7 @@
       </c>
       <c r="AE511" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF511" t="inlineStr">
@@ -58985,7 +58985,7 @@
       </c>
       <c r="AE512" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF512" t="inlineStr">
@@ -59097,7 +59097,7 @@
       </c>
       <c r="AE513" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF513" t="inlineStr">
@@ -59209,7 +59209,7 @@
       </c>
       <c r="AE514" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF514" t="inlineStr">
@@ -59321,7 +59321,7 @@
       </c>
       <c r="AE515" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF515" t="inlineStr">
@@ -59431,7 +59431,7 @@
       </c>
       <c r="AE516" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF516" t="inlineStr">
@@ -59543,7 +59543,7 @@
       </c>
       <c r="AE517" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF517" t="inlineStr">
@@ -59643,7 +59643,7 @@
       </c>
       <c r="AE518" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF518" t="inlineStr">
@@ -59753,7 +59753,7 @@
       </c>
       <c r="AE519" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF519" t="inlineStr">
@@ -59853,7 +59853,7 @@
       </c>
       <c r="AE520" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF520" t="inlineStr">
@@ -59953,7 +59953,7 @@
       </c>
       <c r="AE521" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF521" t="inlineStr">
@@ -60065,7 +60065,7 @@
       </c>
       <c r="AE522" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF522" t="inlineStr">
@@ -60177,7 +60177,7 @@
       </c>
       <c r="AE523" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF523" t="inlineStr">
@@ -60289,7 +60289,7 @@
       </c>
       <c r="AE524" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF524" t="inlineStr">
@@ -60399,7 +60399,7 @@
       </c>
       <c r="AE525" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF525" t="inlineStr">
@@ -60509,7 +60509,7 @@
       </c>
       <c r="AE526" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF526" t="inlineStr">
@@ -60619,7 +60619,7 @@
       </c>
       <c r="AE527" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF527" t="inlineStr">
@@ -60731,7 +60731,7 @@
       </c>
       <c r="AE528" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF528" t="inlineStr">
@@ -60841,7 +60841,7 @@
       </c>
       <c r="AE529" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF529" t="inlineStr">
@@ -60951,7 +60951,7 @@
       </c>
       <c r="AE530" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF530" t="inlineStr">
@@ -61061,7 +61061,7 @@
       </c>
       <c r="AE531" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF531" t="inlineStr">
@@ -61171,7 +61171,7 @@
       </c>
       <c r="AE532" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF532" t="inlineStr">
@@ -61283,7 +61283,7 @@
       </c>
       <c r="AE533" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF533" t="inlineStr">
@@ -61395,7 +61395,7 @@
       </c>
       <c r="AE534" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF534" t="inlineStr">
@@ -61511,7 +61511,7 @@
       </c>
       <c r="AE535" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF535" t="inlineStr">
@@ -61639,7 +61639,7 @@
       </c>
       <c r="AE536" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF536" t="inlineStr">
@@ -61751,7 +61751,7 @@
       </c>
       <c r="AE537" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF537" t="inlineStr">
@@ -61861,7 +61861,7 @@
       </c>
       <c r="AE538" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF538" t="inlineStr">
@@ -61981,7 +61981,7 @@
       </c>
       <c r="AE539" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF539" t="inlineStr">
@@ -62091,7 +62091,7 @@
       </c>
       <c r="AE540" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF540" t="inlineStr">
@@ -62201,7 +62201,7 @@
       </c>
       <c r="AE541" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF541" t="inlineStr">
@@ -62311,7 +62311,7 @@
       </c>
       <c r="AE542" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF542" t="inlineStr">
@@ -62431,7 +62431,7 @@
       </c>
       <c r="AE543" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF543" t="inlineStr">
@@ -62547,7 +62547,7 @@
       </c>
       <c r="AE544" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF544" t="inlineStr">
@@ -62659,7 +62659,7 @@
       </c>
       <c r="AE545" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF545" t="inlineStr">
@@ -62779,7 +62779,7 @@
       </c>
       <c r="AE546" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF546" t="inlineStr">
@@ -62891,7 +62891,7 @@
       </c>
       <c r="AE547" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF547" t="inlineStr">
@@ -62991,7 +62991,7 @@
       </c>
       <c r="AE548" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF548" t="inlineStr">
@@ -63111,7 +63111,7 @@
       </c>
       <c r="AE549" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF549" t="inlineStr">
@@ -63221,7 +63221,7 @@
       </c>
       <c r="AE550" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF550" t="inlineStr">
@@ -63333,7 +63333,7 @@
       </c>
       <c r="AE551" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF551" t="inlineStr">
@@ -63449,7 +63449,7 @@
       </c>
       <c r="AE552" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF552" t="inlineStr">
@@ -63561,7 +63561,7 @@
       </c>
       <c r="AE553" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF553" t="inlineStr">
@@ -63673,7 +63673,7 @@
       </c>
       <c r="AE554" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF554" t="inlineStr">
@@ -63801,7 +63801,7 @@
       </c>
       <c r="AE555" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF555" t="inlineStr">
@@ -63911,7 +63911,7 @@
       </c>
       <c r="AE556" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF556" t="inlineStr">
@@ -64021,7 +64021,7 @@
       </c>
       <c r="AE557" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF557" t="inlineStr">
@@ -64131,7 +64131,7 @@
       </c>
       <c r="AE558" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF558" t="inlineStr">
@@ -64243,7 +64243,7 @@
       </c>
       <c r="AE559" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF559" t="inlineStr">
@@ -64371,7 +64371,7 @@
       </c>
       <c r="AE560" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF560" t="inlineStr">
@@ -64483,7 +64483,7 @@
       </c>
       <c r="AE561" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF561" t="inlineStr">
@@ -64595,7 +64595,7 @@
       </c>
       <c r="AE562" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF562" t="inlineStr">
@@ -64707,7 +64707,7 @@
       </c>
       <c r="AE563" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF563" t="inlineStr">
@@ -64807,7 +64807,7 @@
       </c>
       <c r="AE564" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF564" t="inlineStr">
@@ -64917,7 +64917,7 @@
       </c>
       <c r="AE565" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF565" t="inlineStr">
@@ -65027,7 +65027,7 @@
       </c>
       <c r="AE566" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF566" t="inlineStr">
@@ -65127,7 +65127,7 @@
       </c>
       <c r="AE567" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF567" t="inlineStr">
@@ -65237,7 +65237,7 @@
       </c>
       <c r="AE568" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF568" t="inlineStr">
@@ -65365,7 +65365,7 @@
       </c>
       <c r="AE569" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF569" t="inlineStr">
@@ -65475,7 +65475,7 @@
       </c>
       <c r="AE570" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF570" t="inlineStr">
@@ -65587,7 +65587,7 @@
       </c>
       <c r="AE571" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF571" t="inlineStr">
@@ -65697,7 +65697,7 @@
       </c>
       <c r="AE572" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF572" t="inlineStr">
@@ -65809,7 +65809,7 @@
       </c>
       <c r="AE573" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF573" t="inlineStr">
@@ -65919,7 +65919,7 @@
       </c>
       <c r="AE574" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF574" t="inlineStr">
@@ -66029,7 +66029,7 @@
       </c>
       <c r="AE575" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF575" t="inlineStr">
@@ -66129,7 +66129,7 @@
       </c>
       <c r="AE576" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF576" t="inlineStr">
@@ -66239,7 +66239,7 @@
       </c>
       <c r="AE577" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF577" t="inlineStr">
@@ -66351,7 +66351,7 @@
       </c>
       <c r="AE578" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF578" t="inlineStr">
@@ -66461,7 +66461,7 @@
       </c>
       <c r="AE579" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF579" t="inlineStr">
@@ -66571,7 +66571,7 @@
       </c>
       <c r="AE580" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF580" t="inlineStr">
@@ -66681,7 +66681,7 @@
       </c>
       <c r="AE581" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF581" t="inlineStr">
@@ -66791,7 +66791,7 @@
       </c>
       <c r="AE582" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF582" t="inlineStr">
@@ -66901,7 +66901,7 @@
       </c>
       <c r="AE583" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF583" t="inlineStr">
@@ -67011,7 +67011,7 @@
       </c>
       <c r="AE584" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF584" t="inlineStr">
@@ -67111,7 +67111,7 @@
       </c>
       <c r="AE585" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF585" t="inlineStr">
@@ -67221,7 +67221,7 @@
       </c>
       <c r="AE586" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF586" t="inlineStr">
@@ -67331,7 +67331,7 @@
       </c>
       <c r="AE587" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF587" t="inlineStr">
@@ -67443,7 +67443,7 @@
       </c>
       <c r="AE588" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF588" t="inlineStr">
@@ -67553,7 +67553,7 @@
       </c>
       <c r="AE589" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF589" t="inlineStr">
@@ -67665,7 +67665,7 @@
       </c>
       <c r="AE590" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF590" t="inlineStr">
@@ -67775,7 +67775,7 @@
       </c>
       <c r="AE591" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF591" t="inlineStr">
@@ -67885,7 +67885,7 @@
       </c>
       <c r="AE592" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF592" t="inlineStr">
@@ -67995,7 +67995,7 @@
       </c>
       <c r="AE593" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF593" t="inlineStr">
@@ -68105,7 +68105,7 @@
       </c>
       <c r="AE594" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF594" t="inlineStr">
@@ -68215,7 +68215,7 @@
       </c>
       <c r="AE595" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF595" t="inlineStr">
@@ -68327,7 +68327,7 @@
       </c>
       <c r="AE596" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF596" t="inlineStr">
@@ -68437,7 +68437,7 @@
       </c>
       <c r="AE597" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF597" t="inlineStr">
@@ -68549,7 +68549,7 @@
       </c>
       <c r="AE598" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF598" t="inlineStr">
@@ -68661,7 +68661,7 @@
       </c>
       <c r="AE599" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF599" t="inlineStr">
@@ -68771,7 +68771,7 @@
       </c>
       <c r="AE600" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF600" t="inlineStr">
@@ -68883,7 +68883,7 @@
       </c>
       <c r="AE601" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF601" t="inlineStr">
@@ -68995,7 +68995,7 @@
       </c>
       <c r="AE602" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF602" t="inlineStr">
@@ -69105,7 +69105,7 @@
       </c>
       <c r="AE603" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF603" t="inlineStr">
@@ -69215,7 +69215,7 @@
       </c>
       <c r="AE604" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF604" t="inlineStr">
@@ -69325,7 +69325,7 @@
       </c>
       <c r="AE605" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF605" t="inlineStr">
@@ -69435,7 +69435,7 @@
       </c>
       <c r="AE606" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF606" t="inlineStr">
@@ -69535,7 +69535,7 @@
       </c>
       <c r="AE607" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF607" t="inlineStr">
@@ -69647,7 +69647,7 @@
       </c>
       <c r="AE608" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF608" t="inlineStr">
@@ -69757,7 +69757,7 @@
       </c>
       <c r="AE609" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF609" t="inlineStr">
@@ -69867,7 +69867,7 @@
       </c>
       <c r="AE610" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF610" t="inlineStr">
@@ -69995,7 +69995,7 @@
       </c>
       <c r="AE611" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF611" t="inlineStr">
@@ -70107,7 +70107,7 @@
       </c>
       <c r="AE612" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF612" t="inlineStr">
@@ -70219,7 +70219,7 @@
       </c>
       <c r="AE613" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF613" t="inlineStr">
@@ -70347,7 +70347,7 @@
       </c>
       <c r="AE614" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF614" t="inlineStr">
@@ -70459,7 +70459,7 @@
       </c>
       <c r="AE615" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF615" t="inlineStr">
@@ -70587,7 +70587,7 @@
       </c>
       <c r="AE616" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF616" t="inlineStr">
@@ -70715,7 +70715,7 @@
       </c>
       <c r="AE617" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:41</t>
+          <t>2026-10-06 15:24:20</t>
         </is>
       </c>
       <c r="AF617" t="inlineStr">
@@ -70827,7 +70827,7 @@
       </c>
       <c r="AE618" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF618" t="inlineStr">
@@ -70939,7 +70939,7 @@
       </c>
       <c r="AE619" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF619" t="inlineStr">
@@ -71049,7 +71049,7 @@
       </c>
       <c r="AE620" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF620" t="inlineStr">
@@ -71161,7 +71161,7 @@
       </c>
       <c r="AE621" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF621" t="inlineStr">
@@ -71271,7 +71271,7 @@
       </c>
       <c r="AE622" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF622" t="inlineStr">
@@ -71381,7 +71381,7 @@
       </c>
       <c r="AE623" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF623" t="inlineStr">
@@ -71493,7 +71493,7 @@
       </c>
       <c r="AE624" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF624" t="inlineStr">
@@ -71605,7 +71605,7 @@
       </c>
       <c r="AE625" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF625" t="inlineStr">
@@ -71717,7 +71717,7 @@
       </c>
       <c r="AE626" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF626" t="inlineStr">
@@ -71827,7 +71827,7 @@
       </c>
       <c r="AE627" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF627" t="inlineStr">
@@ -71937,7 +71937,7 @@
       </c>
       <c r="AE628" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF628" t="inlineStr">
@@ -72049,7 +72049,7 @@
       </c>
       <c r="AE629" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF629" t="inlineStr">
@@ -72161,7 +72161,7 @@
       </c>
       <c r="AE630" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF630" t="inlineStr">
@@ -72271,7 +72271,7 @@
       </c>
       <c r="AE631" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF631" t="inlineStr">
@@ -72383,7 +72383,7 @@
       </c>
       <c r="AE632" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF632" t="inlineStr">
@@ -72493,7 +72493,7 @@
       </c>
       <c r="AE633" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF633" t="inlineStr">
@@ -72593,7 +72593,7 @@
       </c>
       <c r="AE634" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF634" t="inlineStr">
@@ -72703,7 +72703,7 @@
       </c>
       <c r="AE635" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF635" t="inlineStr">
@@ -72815,7 +72815,7 @@
       </c>
       <c r="AE636" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF636" t="inlineStr">
@@ -72925,7 +72925,7 @@
       </c>
       <c r="AE637" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF637" t="inlineStr">
@@ -73037,7 +73037,7 @@
       </c>
       <c r="AE638" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF638" t="inlineStr">
@@ -73147,7 +73147,7 @@
       </c>
       <c r="AE639" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF639" t="inlineStr">
@@ -73257,7 +73257,7 @@
       </c>
       <c r="AE640" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF640" t="inlineStr">
@@ -73367,7 +73367,7 @@
       </c>
       <c r="AE641" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF641" t="inlineStr">
@@ -73477,7 +73477,7 @@
       </c>
       <c r="AE642" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF642" t="inlineStr">
@@ -73587,7 +73587,7 @@
       </c>
       <c r="AE643" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF643" t="inlineStr">
@@ -73699,7 +73699,7 @@
       </c>
       <c r="AE644" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF644" t="inlineStr">
@@ -73809,7 +73809,7 @@
       </c>
       <c r="AE645" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF645" t="inlineStr">
@@ -73919,7 +73919,7 @@
       </c>
       <c r="AE646" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF646" t="inlineStr">
@@ -74029,7 +74029,7 @@
       </c>
       <c r="AE647" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF647" t="inlineStr">
@@ -74141,7 +74141,7 @@
       </c>
       <c r="AE648" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF648" t="inlineStr">
@@ -74251,7 +74251,7 @@
       </c>
       <c r="AE649" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF649" t="inlineStr">
@@ -74363,7 +74363,7 @@
       </c>
       <c r="AE650" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF650" t="inlineStr">
@@ -74475,7 +74475,7 @@
       </c>
       <c r="AE651" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF651" t="inlineStr">
@@ -74575,7 +74575,7 @@
       </c>
       <c r="AE652" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF652" t="inlineStr">
@@ -74685,7 +74685,7 @@
       </c>
       <c r="AE653" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF653" t="inlineStr">
@@ -74797,7 +74797,7 @@
       </c>
       <c r="AE654" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF654" t="inlineStr">
@@ -74909,7 +74909,7 @@
       </c>
       <c r="AE655" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF655" t="inlineStr">
@@ -75021,7 +75021,7 @@
       </c>
       <c r="AE656" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF656" t="inlineStr">
@@ -75133,7 +75133,7 @@
       </c>
       <c r="AE657" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF657" t="inlineStr">
@@ -75243,7 +75243,7 @@
       </c>
       <c r="AE658" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF658" t="inlineStr">
@@ -75353,7 +75353,7 @@
       </c>
       <c r="AE659" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF659" t="inlineStr">
@@ -75465,7 +75465,7 @@
       </c>
       <c r="AE660" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF660" t="inlineStr">
@@ -75575,7 +75575,7 @@
       </c>
       <c r="AE661" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF661" t="inlineStr">
@@ -75687,7 +75687,7 @@
       </c>
       <c r="AE662" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF662" t="inlineStr">
@@ -75787,7 +75787,7 @@
       </c>
       <c r="AE663" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF663" t="inlineStr">
@@ -75897,7 +75897,7 @@
       </c>
       <c r="AE664" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF664" t="inlineStr">
@@ -76009,7 +76009,7 @@
       </c>
       <c r="AE665" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF665" t="inlineStr">
@@ -76119,7 +76119,7 @@
       <c r="AD666" t="inlineStr"/>
       <c r="AE666" t="inlineStr">
         <is>
-          <t>2026-10-06 10:43:02</t>
+          <t>2026-10-06 15:24:42</t>
         </is>
       </c>
       <c r="AF666" t="inlineStr">
@@ -76231,7 +76231,7 @@
       </c>
       <c r="AE667" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF667" t="inlineStr">
@@ -76343,7 +76343,7 @@
       </c>
       <c r="AE668" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF668" t="inlineStr">
@@ -76453,7 +76453,7 @@
       </c>
       <c r="AE669" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF669" t="inlineStr">
@@ -76565,7 +76565,7 @@
       </c>
       <c r="AE670" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF670" t="inlineStr">
@@ -76665,7 +76665,7 @@
       </c>
       <c r="AE671" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF671" t="inlineStr">
@@ -76765,7 +76765,7 @@
       </c>
       <c r="AE672" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF672" t="inlineStr">
@@ -76865,7 +76865,7 @@
       </c>
       <c r="AE673" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF673" t="inlineStr">
@@ -76977,7 +76977,7 @@
       </c>
       <c r="AE674" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF674" t="inlineStr">
@@ -77077,7 +77077,7 @@
       </c>
       <c r="AE675" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF675" t="inlineStr">
@@ -77187,7 +77187,7 @@
       </c>
       <c r="AE676" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF676" t="inlineStr">
@@ -77287,7 +77287,7 @@
       </c>
       <c r="AE677" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF677" t="inlineStr">
@@ -77399,7 +77399,7 @@
       </c>
       <c r="AE678" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF678" t="inlineStr">
@@ -77511,7 +77511,7 @@
       </c>
       <c r="AE679" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF679" t="inlineStr">
@@ -77623,7 +77623,7 @@
       </c>
       <c r="AE680" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF680" t="inlineStr">
@@ -77735,7 +77735,7 @@
       </c>
       <c r="AE681" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF681" t="inlineStr">
@@ -77835,7 +77835,7 @@
       </c>
       <c r="AE682" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF682" t="inlineStr">
@@ -77947,7 +77947,7 @@
       </c>
       <c r="AE683" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF683" t="inlineStr">
@@ -78057,7 +78057,7 @@
       </c>
       <c r="AE684" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF684" t="inlineStr">
@@ -78169,7 +78169,7 @@
       </c>
       <c r="AE685" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF685" t="inlineStr">
@@ -78269,7 +78269,7 @@
       </c>
       <c r="AE686" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF686" t="inlineStr">
@@ -78369,7 +78369,7 @@
       </c>
       <c r="AE687" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF687" t="inlineStr">
@@ -78469,7 +78469,7 @@
       </c>
       <c r="AE688" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF688" t="inlineStr">
@@ -78569,7 +78569,7 @@
       </c>
       <c r="AE689" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF689" t="inlineStr">
@@ -78681,7 +78681,7 @@
       </c>
       <c r="AE690" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF690" t="inlineStr">
@@ -78793,7 +78793,7 @@
       </c>
       <c r="AE691" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF691" t="inlineStr">
@@ -78893,7 +78893,7 @@
       </c>
       <c r="AE692" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF692" t="inlineStr">
@@ -79003,7 +79003,7 @@
       </c>
       <c r="AE693" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF693" t="inlineStr">
@@ -79115,7 +79115,7 @@
       </c>
       <c r="AE694" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF694" t="inlineStr">
@@ -79227,7 +79227,7 @@
       </c>
       <c r="AE695" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF695" t="inlineStr">
@@ -79339,7 +79339,7 @@
       </c>
       <c r="AE696" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF696" t="inlineStr">
@@ -79451,7 +79451,7 @@
       </c>
       <c r="AE697" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF697" t="inlineStr">
@@ -79563,7 +79563,7 @@
       </c>
       <c r="AE698" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF698" t="inlineStr">
@@ -79675,7 +79675,7 @@
       </c>
       <c r="AE699" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF699" t="inlineStr">
@@ -79787,7 +79787,7 @@
       </c>
       <c r="AE700" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF700" t="inlineStr">
@@ -79887,7 +79887,7 @@
       </c>
       <c r="AE701" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF701" t="inlineStr">
@@ -79987,7 +79987,7 @@
       </c>
       <c r="AE702" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF702" t="inlineStr">
@@ -80099,7 +80099,7 @@
       </c>
       <c r="AE703" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:36</t>
+          <t>2026-10-06 15:24:14</t>
         </is>
       </c>
       <c r="AF703" t="inlineStr">
@@ -80199,7 +80199,7 @@
       </c>
       <c r="AE704" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF704" t="inlineStr">
@@ -80299,7 +80299,7 @@
       </c>
       <c r="AE705" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF705" t="inlineStr">
@@ -80399,7 +80399,7 @@
       </c>
       <c r="AE706" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF706" t="inlineStr">
@@ -80509,7 +80509,7 @@
       </c>
       <c r="AE707" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF707" t="inlineStr">
@@ -80609,7 +80609,7 @@
       </c>
       <c r="AE708" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF708" t="inlineStr">
@@ -80719,7 +80719,7 @@
       </c>
       <c r="AE709" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF709" t="inlineStr">
@@ -80801,7 +80801,7 @@
       <c r="AD710" t="inlineStr"/>
       <c r="AE710" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF710" t="inlineStr">
@@ -80883,7 +80883,7 @@
       <c r="AD711" t="inlineStr"/>
       <c r="AE711" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF711" t="inlineStr">
@@ -80965,7 +80965,7 @@
       <c r="AD712" t="inlineStr"/>
       <c r="AE712" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF712" t="inlineStr">
@@ -81047,7 +81047,7 @@
       <c r="AD713" t="inlineStr"/>
       <c r="AE713" t="inlineStr">
         <is>
-          <t>2026-10-06 10:42:45</t>
+          <t>2026-10-06 15:24:25</t>
         </is>
       </c>
       <c r="AF713" t="inlineStr">
